--- a/data/official_data/knowledge/scholarships.xlsx
+++ b/data/official_data/knowledge/scholarships.xlsx
@@ -440,7 +440,7 @@
   <dimension ref="A1:F8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.42578125" customWidth="1"/>
+    <col min="1" max="1" width="12.5703125" customWidth="1"/>
     <col min="2" max="2" width="12.28515625" customWidth="1"/>
     <col min="3" max="3" width="32" customWidth="1"/>
     <col min="4" max="4" width="18.85546875" customWidth="1"/>
